--- a/output_2a.xlsx
+++ b/output_2a.xlsx
@@ -460,10 +460,10 @@
         <v>32500</v>
       </c>
       <c r="D2" t="n">
-        <v>56952</v>
+        <v>56970</v>
       </c>
       <c r="E2" t="n">
-        <v>89452</v>
+        <v>89470</v>
       </c>
     </row>
     <row r="3">
@@ -593,10 +593,10 @@
         <v>145500</v>
       </c>
       <c r="D9" t="n">
-        <v>394970.8</v>
+        <v>394988.8</v>
       </c>
       <c r="E9" t="n">
-        <v>540470.8</v>
+        <v>540488.8</v>
       </c>
     </row>
   </sheetData>
@@ -664,13 +664,13 @@
         <v>81.2</v>
       </c>
       <c r="E2" t="n">
-        <v>9936</v>
+        <v>9948</v>
       </c>
       <c r="F2" t="n">
         <v>10000</v>
       </c>
       <c r="G2" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="3">
@@ -678,16 +678,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>800</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F3" t="n">
         <v>10000</v>
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F4" t="n">
         <v>10000</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F6" t="n">
         <v>10000</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F7" t="n">
         <v>10000</v>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F8" t="n">
         <v>10000</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F11" t="n">
         <v>10000</v>
@@ -885,16 +885,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C12" t="n">
         <v>800</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F12" t="n">
         <v>10000</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F13" t="n">
         <v>10000</v>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F14" t="n">
         <v>10000</v>
@@ -1009,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F17" t="n">
         <v>10000</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F18" t="n">
         <v>10000</v>
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>10000</v>
+        <v>9999</v>
       </c>
       <c r="F19" t="n">
         <v>10000</v>
@@ -1069,13 +1069,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C20" t="n">
         <v>800</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E20" t="n">
         <v>8168</v>
@@ -1115,13 +1115,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C22" t="n">
         <v>800</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1184,13 +1184,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C25" t="n">
         <v>800</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1230,13 +1230,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C27" t="n">
         <v>800</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1253,13 +1253,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C28" t="n">
         <v>800</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C29" t="n">
         <v>800</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1299,13 +1299,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C30" t="n">
         <v>800</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1518,25 +1518,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3312</v>
+        <v>3316</v>
       </c>
       <c r="C2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="D2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="G2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="H2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1545,16 +1545,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="L2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="M2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="N2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1563,13 +1563,13 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="R2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="S2" t="n">
-        <v>3333.3</v>
+        <v>3333</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -2477,55 +2477,55 @@
         <v>6400</v>
       </c>
       <c r="F2" t="n">
-        <v>9712</v>
+        <v>9716</v>
       </c>
       <c r="G2" t="n">
-        <v>1045.3</v>
+        <v>1049</v>
       </c>
       <c r="H2" t="n">
-        <v>4378.7</v>
+        <v>4382</v>
       </c>
       <c r="I2" t="n">
-        <v>4378.7</v>
+        <v>4382</v>
       </c>
       <c r="J2" t="n">
-        <v>7712</v>
+        <v>7715</v>
       </c>
       <c r="K2" t="n">
-        <v>11045.3</v>
+        <v>11048</v>
       </c>
       <c r="L2" t="n">
-        <v>1578.7</v>
+        <v>1581</v>
       </c>
       <c r="M2" t="n">
-        <v>1578.7</v>
+        <v>1581</v>
       </c>
       <c r="N2" t="n">
-        <v>1578.7</v>
+        <v>1581</v>
       </c>
       <c r="O2" t="n">
-        <v>4912</v>
+        <v>4914</v>
       </c>
       <c r="P2" t="n">
-        <v>8245.299999999999</v>
+        <v>8247</v>
       </c>
       <c r="Q2" t="n">
-        <v>11578.7</v>
+        <v>11580</v>
       </c>
       <c r="R2" t="n">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="S2" t="n">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="T2" t="n">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="U2" t="n">
-        <v>5445.3</v>
+        <v>5446</v>
       </c>
       <c r="V2" t="n">
-        <v>8778.700000000001</v>
+        <v>8779</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>

--- a/output_2a.xlsx
+++ b/output_2a.xlsx
@@ -678,13 +678,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>800</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>9999</v>
@@ -885,13 +885,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>800</v>
       </c>
       <c r="D12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>9999</v>
@@ -1069,13 +1069,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>800</v>
       </c>
       <c r="D20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>8168</v>
@@ -1115,13 +1115,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>800</v>
       </c>
       <c r="D22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1184,13 +1184,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>800</v>
       </c>
       <c r="D25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1230,13 +1230,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>800</v>
       </c>
       <c r="D27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1253,13 +1253,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>800</v>
       </c>
       <c r="D28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>800</v>
       </c>
       <c r="D29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1299,13 +1299,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>800</v>
       </c>
       <c r="D30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/output_2a.xlsx
+++ b/output_2a.xlsx
@@ -678,13 +678,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>800</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
         <v>9999</v>
@@ -885,13 +885,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C12" t="n">
         <v>800</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
         <v>9999</v>
@@ -1069,13 +1069,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C20" t="n">
         <v>800</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E20" t="n">
         <v>8168</v>
@@ -1115,13 +1115,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C22" t="n">
         <v>800</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1184,13 +1184,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C25" t="n">
         <v>800</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1230,13 +1230,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C27" t="n">
         <v>800</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1253,13 +1253,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C28" t="n">
         <v>800</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C29" t="n">
         <v>800</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1299,13 +1299,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C30" t="n">
         <v>800</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
